--- a/sub_pro_16_wc_2026_pred/datasets/tsi_3_prediction.xlsx
+++ b/sub_pro_16_wc_2026_pred/datasets/tsi_3_prediction.xlsx
@@ -383,7 +383,7 @@
         </is>
       </c>
       <c r="C2">
-        <v>0.08299388456373037</v>
+        <v>0.0796210588089758</v>
       </c>
     </row>
     <row r="3">
@@ -398,7 +398,7 @@
         </is>
       </c>
       <c r="C3">
-        <v>-0.7113830092454801</v>
+        <v>-0.7158913132251642</v>
       </c>
     </row>
     <row r="4">
@@ -413,7 +413,7 @@
         </is>
       </c>
       <c r="C4">
-        <v>-0.2519285256400665</v>
+        <v>-0.2586102062692365</v>
       </c>
     </row>
     <row r="5">
@@ -428,7 +428,7 @@
         </is>
       </c>
       <c r="C5">
-        <v>-0.5354159808197011</v>
+        <v>-0.543432193762608</v>
       </c>
     </row>
     <row r="6">
@@ -443,7 +443,7 @@
         </is>
       </c>
       <c r="C6">
-        <v>-0.2953914758788622</v>
+        <v>-0.3079965575942725</v>
       </c>
     </row>
     <row r="7">
@@ -458,7 +458,7 @@
         </is>
       </c>
       <c r="C7">
-        <v>-0.5750988551605672</v>
+        <v>-0.5824608166112183</v>
       </c>
     </row>
     <row r="8">
@@ -473,7 +473,7 @@
         </is>
       </c>
       <c r="C8">
-        <v>-0.6393967995598809</v>
+        <v>-0.6403259410178533</v>
       </c>
     </row>
     <row r="9">
@@ -488,7 +488,7 @@
         </is>
       </c>
       <c r="C9">
-        <v>0.2159142676274897</v>
+        <v>0.2071564540428741</v>
       </c>
     </row>
     <row r="10">
@@ -503,7 +503,7 @@
         </is>
       </c>
       <c r="C10">
-        <v>1.156458976875824</v>
+        <v>1.154600232596675</v>
       </c>
     </row>
     <row r="11">
@@ -518,7 +518,7 @@
         </is>
       </c>
       <c r="C11">
-        <v>0.1818523810663203</v>
+        <v>0.1773328429323777</v>
       </c>
     </row>
     <row r="12">
@@ -533,7 +533,7 @@
         </is>
       </c>
       <c r="C12">
-        <v>-0.5452817070898198</v>
+        <v>-0.5473133803567041</v>
       </c>
     </row>
     <row r="13">
@@ -548,7 +548,7 @@
         </is>
       </c>
       <c r="C13">
-        <v>-0.3267467096937239</v>
+        <v>-0.3345133861578001</v>
       </c>
     </row>
     <row r="14">
@@ -563,7 +563,7 @@
         </is>
       </c>
       <c r="C14">
-        <v>0.5912375559482701</v>
+        <v>0.583559013064243</v>
       </c>
     </row>
     <row r="15">
@@ -578,7 +578,7 @@
         </is>
       </c>
       <c r="C15">
-        <v>-0.2175467528480173</v>
+        <v>-0.2199559522572894</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="C16">
-        <v>-0.2999570005311768</v>
+        <v>-0.05824795796699984</v>
       </c>
     </row>
     <row r="17">
@@ -608,7 +608,7 @@
         </is>
       </c>
       <c r="C17">
-        <v>-0.05341210040179162</v>
+        <v>-0.06031226222357196</v>
       </c>
     </row>
     <row r="18">
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="C18">
-        <v>0.5655536434838676</v>
+        <v>0.5579013146649422</v>
       </c>
     </row>
     <row r="19">
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="C19">
-        <v>-0.5319981266827117</v>
+        <v>-0.5327651237213344</v>
       </c>
     </row>
     <row r="20">
@@ -653,7 +653,7 @@
         </is>
       </c>
       <c r="C20">
-        <v>0.02575028711057045</v>
+        <v>0.02439554378277389</v>
       </c>
     </row>
     <row r="21">
@@ -668,7 +668,7 @@
         </is>
       </c>
       <c r="C21">
-        <v>0.05192914125511496</v>
+        <v>0.04861155534979229</v>
       </c>
     </row>
     <row r="22">
@@ -683,7 +683,7 @@
         </is>
       </c>
       <c r="C22">
-        <v>0.6350354789738183</v>
+        <v>0.6277367535297385</v>
       </c>
     </row>
     <row r="23">
@@ -698,7 +698,7 @@
         </is>
       </c>
       <c r="C23">
-        <v>0.1898932941876626</v>
+        <v>0.1798947361164542</v>
       </c>
     </row>
     <row r="24">
@@ -713,7 +713,7 @@
         </is>
       </c>
       <c r="C24">
-        <v>-0.1986918520574826</v>
+        <v>-0.208644930095248</v>
       </c>
     </row>
     <row r="25">
@@ -728,7 +728,7 @@
         </is>
       </c>
       <c r="C25">
-        <v>-0.4921815383405533</v>
+        <v>-0.4958371704014407</v>
       </c>
     </row>
     <row r="26">
@@ -743,7 +743,7 @@
         </is>
       </c>
       <c r="C26">
-        <v>0.2971843005133121</v>
+        <v>0.2899471530379887</v>
       </c>
     </row>
     <row r="27">
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="C27">
-        <v>-0.3218802743645142</v>
+        <v>-0.3245935943247656</v>
       </c>
     </row>
     <row r="28">
@@ -773,7 +773,7 @@
         </is>
       </c>
       <c r="C28">
-        <v>-0.3929954518255913</v>
+        <v>-0.3974617762641168</v>
       </c>
     </row>
     <row r="29">
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="C29">
-        <v>-0.6894364340065068</v>
+        <v>-0.6967593315644282</v>
       </c>
     </row>
     <row r="30">
@@ -803,7 +803,7 @@
         </is>
       </c>
       <c r="C30">
-        <v>1.429901797830649</v>
+        <v>1.423518324939683</v>
       </c>
     </row>
     <row r="31">
@@ -818,7 +818,7 @@
         </is>
       </c>
       <c r="C31">
-        <v>-0.5021680652243766</v>
+        <v>-0.5050815165177276</v>
       </c>
     </row>
     <row r="32">
@@ -833,7 +833,7 @@
         </is>
       </c>
       <c r="C32">
-        <v>-0.6265793181571776</v>
+        <v>-0.6282739368401592</v>
       </c>
     </row>
     <row r="33">
@@ -848,7 +848,7 @@
         </is>
       </c>
       <c r="C33">
-        <v>0.09511983188272075</v>
+        <v>0.09054517816084781</v>
       </c>
     </row>
     <row r="34">
@@ -863,7 +863,7 @@
         </is>
       </c>
       <c r="C34">
-        <v>1.678555260074007</v>
+        <v>1.671668267417351</v>
       </c>
     </row>
     <row r="35">
@@ -878,7 +878,7 @@
         </is>
       </c>
       <c r="C35">
-        <v>0.2161249745454016</v>
+        <v>0.2155368849454782</v>
       </c>
     </row>
     <row r="36">
@@ -893,7 +893,7 @@
         </is>
       </c>
       <c r="C36">
-        <v>-0.5095319249866413</v>
+        <v>-0.5123051978998184</v>
       </c>
     </row>
     <row r="37">
@@ -908,7 +908,7 @@
         </is>
       </c>
       <c r="C37">
-        <v>0.2206684436837993</v>
+        <v>0.2103483831514676</v>
       </c>
     </row>
     <row r="38">
@@ -923,7 +923,7 @@
         </is>
       </c>
       <c r="C38">
-        <v>0.9474393308868236</v>
+        <v>0.9411744339893375</v>
       </c>
     </row>
     <row r="39">
@@ -938,7 +938,7 @@
         </is>
       </c>
       <c r="C39">
-        <v>-0.1120108279845666</v>
+        <v>-0.1145374203365959</v>
       </c>
     </row>
     <row r="40">
@@ -953,7 +953,7 @@
         </is>
       </c>
       <c r="C40">
-        <v>-0.1260082021453316</v>
+        <v>-0.1344245667879475</v>
       </c>
     </row>
     <row r="41">
@@ -968,7 +968,7 @@
         </is>
       </c>
       <c r="C41">
-        <v>-0.6332170774397331</v>
+        <v>-0.6370520163734649</v>
       </c>
     </row>
     <row r="42">
@@ -983,7 +983,7 @@
         </is>
       </c>
       <c r="C42">
-        <v>0.994308833510362</v>
+        <v>0.9889550087893502</v>
       </c>
     </row>
     <row r="43">
@@ -998,7 +998,7 @@
         </is>
       </c>
       <c r="C43">
-        <v>-0.1561276916532448</v>
+        <v>-0.1583775742919181</v>
       </c>
     </row>
     <row r="44">
@@ -1013,7 +1013,7 @@
         </is>
       </c>
       <c r="C44">
-        <v>-0.6212093239603557</v>
+        <v>-0.6276010055544098</v>
       </c>
     </row>
     <row r="45">
@@ -1028,7 +1028,7 @@
         </is>
       </c>
       <c r="C45">
-        <v>0.2760426404958962</v>
+        <v>0.2740305894659549</v>
       </c>
     </row>
     <row r="46">
@@ -1043,7 +1043,7 @@
         </is>
       </c>
       <c r="C46">
-        <v>1.086185438206748</v>
+        <v>1.078401867480449</v>
       </c>
     </row>
     <row r="47">
@@ -1058,7 +1058,7 @@
         </is>
       </c>
       <c r="C47">
-        <v>0.04852647613978738</v>
+        <v>0.04175490162104702</v>
       </c>
     </row>
     <row r="48">
@@ -1073,7 +1073,7 @@
         </is>
       </c>
       <c r="C48">
-        <v>-0.3622245012887269</v>
+        <v>-0.3632664316246408</v>
       </c>
     </row>
     <row r="49">
@@ -1088,7 +1088,7 @@
         </is>
       </c>
       <c r="C49">
-        <v>-0.2588567118755782</v>
+        <v>-0.2606489378470705</v>
       </c>
     </row>
   </sheetData>
